--- a/input/timetable/Магистратура_АФК_.xlsx
+++ b/input/timetable/Магистратура_АФК_.xlsx
@@ -1630,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>

--- a/input/timetable/Магистратура_АФК_.xlsx
+++ b/input/timetable/Магистратура_АФК_.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24045" windowHeight="9135"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24045" windowHeight="9135" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>пара</t>
   </si>
@@ -75,6 +75,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -111,6 +114,12 @@
     <t>Психологические основы адаптивной физической культуры и спорта (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Шнейдер В.Ю.</t>
+  </si>
+  <si>
+    <t>Солодилов Р.О.</t>
+  </si>
+  <si>
     <t>//История и методология науки (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -123,6 +132,9 @@
     <t>Физическая культура в специальной медицинской группе образовательных организаций высшего образования (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Воронюк Т.В.</t>
+  </si>
+  <si>
     <t>Современные проблемы и перспективы развития адаптивной физической культуры (лек), ЭОиДОТ// Инновационные технологии в лечебной физической культуре (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -138,6 +150,9 @@
     <t>ФТД: Современные методы оценки влияния физических нагрузок на организм занимающихся адаптивной физической культурой (пр), ЭОиДОТ//  Производственная практика, профессионально-ориентированная практика, ЭОиДОТ</t>
   </si>
   <si>
+    <t>Мальков М.Н./Юденко И.Э.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -159,12 +174,18 @@
     <t>Физическая реабилитация и оздоровление в адаптивном физическом воспитаниии спорте (ТО: 02.02.2026 -09.03.2026)</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Соревновательная деятельность в адаптивной физической культуре и спорте (лек), К210// Практикум по межкультурной коммуникации, ЭОиДОТ</t>
   </si>
   <si>
     <t>Соревновательная деятельность в адаптивной физической культуре и спорте (пр), К210// Практикум по межкультурной коммуникации, ЭОиДОТ</t>
   </si>
   <si>
+    <t>Жулепов В.И./Побережник Д.А.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
@@ -172,6 +193,9 @@
   </si>
   <si>
     <t>Адаптивная физическая культура в геронтологии (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Юденко И.Э.</t>
   </si>
   <si>
     <t>Психологические основы адаптивной физической культуры и спорта (лек), ЭОиДОТ</t>
@@ -275,7 +299,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,12 +318,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -379,6 +409,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -627,6 +715,21 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -699,10 +802,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -717,7 +842,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -757,28 +882,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -787,6 +915,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
@@ -806,114 +935,124 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1224,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1233,10 +1372,11 @@
     <col min="4" max="4" width="19.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1244,15 +1384,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1260,13 +1400,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1276,27 +1416,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
+      <c r="C7" s="37" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -1306,35 +1446,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="68"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -1345,231 +1485,277 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="25">
         <v>5</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="57"/>
       <c r="E11" s="57"/>
       <c r="F11" s="58"/>
-    </row>
-    <row r="12" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="G11" s="46"/>
+    </row>
+    <row r="12" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>6</v>
       </c>
-      <c r="C12" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="52"/>
-      <c r="L12" s="42"/>
-    </row>
-    <row r="13" spans="1:12" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="52"/>
+    </row>
+    <row r="13" spans="1:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>7</v>
       </c>
-      <c r="C13" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="24">
+      <c r="C13" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="54" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="25">
         <v>6</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="57"/>
       <c r="E14" s="57"/>
       <c r="F14" s="58"/>
-    </row>
-    <row r="15" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="G14" s="38"/>
+    </row>
+    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <v>7</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52"/>
-    </row>
-    <row r="16" spans="1:12" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="30"/>
-      <c r="B16" s="28">
+      <c r="C15" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="32"/>
+      <c r="B16" s="30">
         <v>8</v>
       </c>
-      <c r="C16" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="24">
+      <c r="C16" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="25">
         <v>6</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="64"/>
-    </row>
-    <row r="18" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C17" s="75"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <v>7</v>
       </c>
-      <c r="C18" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="52"/>
-    </row>
-    <row r="19" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="30"/>
-      <c r="B19" s="28">
+      <c r="C18" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="32"/>
+      <c r="B19" s="30">
         <v>8</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="55"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="24">
+      <c r="C19" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="25">
         <v>6</v>
       </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="64"/>
-    </row>
-    <row r="21" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="75"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="28"/>
+    </row>
+    <row r="21" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>7</v>
       </c>
-      <c r="C21" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
-    </row>
-    <row r="22" spans="1:6" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="28">
+      <c r="C21" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="30">
         <v>8</v>
       </c>
-      <c r="C22" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="24">
+      <c r="C22" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="25">
         <v>6</v>
       </c>
       <c r="C23" s="56"/>
       <c r="D23" s="57"/>
       <c r="E23" s="57"/>
       <c r="F23" s="58"/>
-    </row>
-    <row r="24" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="31"/>
-      <c r="B24" s="26">
+      <c r="G23" s="38"/>
+    </row>
+    <row r="24" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="27">
         <v>7</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="34"/>
+      <c r="B25" s="30">
+        <v>8</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="36">
+        <v>2</v>
+      </c>
+      <c r="C26" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52"/>
-    </row>
-    <row r="25" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="28">
-        <v>8</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="34">
-        <v>2</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="67"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="40"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="45"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="49"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="45"/>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
@@ -1577,7 +1763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
         <v>17</v>
       </c>
@@ -1587,11 +1773,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C9:F9"/>
@@ -1608,6 +1789,11 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -1639,10 +1825,11 @@
     <col min="4" max="4" width="19.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1650,15 +1837,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1666,13 +1853,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1682,27 +1869,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
+      <c r="C7" s="37" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -1712,35 +1899,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="68"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -1751,202 +1938,230 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="46"/>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>6</v>
       </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="64"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="75"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="28"/>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>7</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="24">
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="47"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="25">
         <v>6</v>
       </c>
-      <c r="C14" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-    </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C14" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="38"/>
+    </row>
+    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <v>7</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="64"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="30"/>
-      <c r="B16" s="28">
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="28"/>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="32"/>
+      <c r="B16" s="30">
         <v>8</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="34">
+      <c r="C16" s="84"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="47"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="36">
         <v>5</v>
       </c>
-      <c r="C17" s="75"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
-    </row>
-    <row r="18" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C17" s="87"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="38"/>
+    </row>
+    <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <v>6</v>
       </c>
-      <c r="C18" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="52"/>
-    </row>
-    <row r="19" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="30"/>
-      <c r="B19" s="28">
+      <c r="C18" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="32"/>
+      <c r="B19" s="30">
         <v>7</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="55"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="24">
+      <c r="C19" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="25">
         <v>5</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="81"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="53"/>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>6</v>
       </c>
-      <c r="C21" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
-    </row>
-    <row r="22" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="28">
+      <c r="C21" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="30">
         <v>7</v>
       </c>
-      <c r="C22" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="24">
+      <c r="C22" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="25">
         <v>6</v>
       </c>
-      <c r="C23" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="71"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="31"/>
-      <c r="B24" s="26">
+      <c r="C23" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="38"/>
+    </row>
+    <row r="24" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="27">
         <v>7</v>
       </c>
-      <c r="C24" s="62"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="64"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="28">
+      <c r="C24" s="75"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="28"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="34"/>
+      <c r="B25" s="30">
         <v>8</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="34">
+      <c r="C25" s="84"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="47"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="36">
         <v>2</v>
       </c>
-      <c r="C26" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71"/>
-    </row>
-    <row r="27" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="67"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C26" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="48"/>
+    </row>
+    <row r="27" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="49"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
@@ -1954,7 +2169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
@@ -1964,13 +2179,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:F9"/>
@@ -1983,6 +2191,13 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">
